--- a/artfynd/A 21931-2026 artfynd.xlsx
+++ b/artfynd/A 21931-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97904188</v>
+        <v>116535579</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83204</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>779</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lindskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Holwaya mucida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schulzer) Korf &amp; Abawi</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>anamorf</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Båstebacken söder om, Vg</t>
+          <t>Fredriksberg, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442342.0027825498</v>
+        <v>442327</v>
       </c>
       <c r="R2" t="n">
-        <v>6505378.178499145</v>
+        <v>6505453</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,27 +747,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,18 +761,34 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>skogslind</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Tilia cordata</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Tilia cordata</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Björn Bråvander, Carina Lerdahl</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -795,12 +798,7 @@
         <v>99140943</v>
       </c>
       <c r="B3" t="n">
-        <v>89940</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442008.1040014409</v>
+        <v>442008</v>
       </c>
       <c r="R3" t="n">
-        <v>6505482.453032603</v>
+        <v>6505482</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -865,19 +863,9 @@
           <t>2022-03-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-03-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -912,12 +900,7 @@
         <v>112662068</v>
       </c>
       <c r="B4" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,15 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116535579</v>
+        <v>118753932</v>
       </c>
       <c r="B5" t="n">
-        <v>82076</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,30 +1024,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>779</v>
+        <v>3884</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lindskål</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Holwaya mucida</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schulzer) Korf &amp; Abawi</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>anamorf</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1077,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>442327</v>
+        <v>442352</v>
       </c>
       <c r="R5" t="n">
-        <v>6505453</v>
+        <v>6505406</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,12 +1081,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,21 +1098,6 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>skogslind</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Tilia cordata</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Tilia cordata</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1155,15 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118753932</v>
+        <v>5038093</v>
       </c>
       <c r="B6" t="n">
-        <v>91067</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,40 +1125,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3884</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fredriksberg, Vg</t>
+          <t>BÅSTEBACKEN (09D1j03), Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>442352</v>
+        <v>442166</v>
       </c>
       <c r="R6" t="n">
-        <v>6505406</v>
+        <v>6505422</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1228,12 +1179,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>1993-10-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>1993-10-08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>090319031 / HEPA NOB / Enstaka-sparsam (1)  / OBJ.AREA:1,8 ha</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,34 +1198,37 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Hassellund / Lövängsrest</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Björn Bråvander, Carina Lerdahl</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Bo Kindbom</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118753941</v>
+        <v>97904188</v>
       </c>
       <c r="B7" t="n">
-        <v>100119</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,20 +1254,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fredriksberg, Vg</t>
+          <t>Båstebacken söder om, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>442352</v>
+        <v>442342</v>
       </c>
       <c r="R7" t="n">
-        <v>6505406</v>
+        <v>6505378</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,12 +1290,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2022-01-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,22 +1309,265 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>118753941</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fredriksberg, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>442352</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6505406</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Töreboda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bäck</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Björn Bråvander</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Björn Bråvander, Carina Lerdahl</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>114435070</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91444</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>233192</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Solfingersvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ramaria thalliovirescens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Franchi &amp; M.Marchetti</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Fredriksberg, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>442382</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6505373</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Töreboda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bäck</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-08-26</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-08-26</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Syn. Ramaria thalliovirescens</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>barcode</t>
+        </is>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Under lind och hassel</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>BB-372</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Björn Bråvander, Carina Lerdahl</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Fynd med DNA-sekvens - 1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
